--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260608.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>316,723,368</t>
+          <t>63,127,494</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>63,127,494</t>
+          <t>316,723,368</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>64,391,147</t>
+          <t>101,677,963</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>101,677,963</t>
+          <t>64,391,147</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>262,073,400</t>
+          <t>1,177,430</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,177,430</t>
+          <t>262,073,400</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>223,924,732</t>
+          <t>1,738,619</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,738,619</t>
+          <t>22,443,866</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>22,443,866</t>
+          <t>223,924,732</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>22,421,429</t>
+          <t>215,944,647</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>215,944,647</t>
+          <t>22,421,429</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>9,474,385</t>
+          <t>230,659,732</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>230,659,732</t>
+          <t>9,474,385</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202606NYF</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>台灣50ETF股票期貨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,738</t>
+          <t>19,908,507</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>202606NYF</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>台灣50ETF股票期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>19,908,507</t>
+          <t>1,738</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
